--- a/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="estab_Video_583_EXP6_CTRL4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="resumen_Video_583_EXP6_CTR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ritmo_Video_583_EXP6_CTRL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="grilla_Video_583_EXP6_CTR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="eventos_Video_583_EXP6_CTR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_583_EXP6_CTRL4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_583_EXP6_CTR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_583_EXP6_CTRL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_583_EXP6_CTR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_583_EXP6_CTR" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,22 +421,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -459,13 +447,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.2277</v>
+        <v>0.2175</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -473,7 +461,7 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3036</v>
+        <v>0.29</v>
       </c>
       <c r="C3" t="n">
         <v>14</v>
@@ -487,13 +475,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4555</v>
+        <v>0.435</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -501,10 +489,10 @@
         <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>0.6073</v>
+        <v>0.58</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -515,10 +503,10 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.7591</v>
+        <v>0.725</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -529,10 +517,10 @@
         <v>12</v>
       </c>
       <c r="B7" t="n">
-        <v>0.9109</v>
+        <v>0.87</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -543,7 +531,7 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>1.1386</v>
+        <v>1.0875</v>
       </c>
       <c r="C8" t="n">
         <v>6</v>
@@ -557,7 +545,7 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>1.5182</v>
+        <v>1.45</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
@@ -577,106 +565,136 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:Z2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>k_usado</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>k_automatico</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>hay_meseta</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>meseta_motivo</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>meseta_k_rango</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>conteo_reportable</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>picos_con_sep_menor</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
@@ -689,75 +707,95 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29.67353799876205</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="C2" t="n">
         <v>2236</v>
       </c>
       <c r="D2" t="n">
-        <v>75.31963327370305</v>
+        <v>75.32000000000002</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07590911999999164</v>
+        <v>0.07249914000000485</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1512057381725957</v>
+        <v>0.1165306153195274</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>12</v>
       </c>
-      <c r="J2" t="n">
-        <v>10.11001788908766</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.08929999999998</v>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>{'n_eventos': 7, 'hay_estimulacion': True, 'estimulados': array([0, 1, 2, 3, 4]), 'espontaneos': array([], dtype=int64), 'jitter_limitado_por_resolucion': True, 'z': 17.248, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 10.1179, 'periodo_s': 10.10665, 'periodo_err_s': 0.00308, 'frecuencia_Hz': 0.09894, 'frecuencia_err_Hz': 3e-05, 'jitter_s': np.float64(0.00973), 'tolerancia_s': 0.0674, 'n_estimulados': 5, 'n_ranuras': 5, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 10.818, 'tren_fin_s': 51.258, 'estimulados_dudosos': array([5, 6]), 'n_estimulados_dudosos': 2, 'dudosos':    indice_evento  tiempo_s  ranura  desvio_s
-0              5    61.132       6   -0.2325
-1              6    72.253       7    0.7818, 'resumen_grupos':                  grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
-0          estimulados  5  ...               3.0893           0.0741
-1  estimulados_dudosos  2  ...               2.0870           1.0584
-[2 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
+          <t>meseta de 6 eventos en k=12..20 (3 puntos) con 0 falsos de control</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>12-20</t>
+        </is>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>8</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10.00166666666666</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.095449999999971</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>{'n_eventos': 6, 'hay_estimulacion': True, 'estimulados': array([0, 1, 2, 3, 4, 5]), 'espontaneos': array([], dtype=int64), 'z': 15.815, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 10.0169, 'periodo_s': 10.00119, 'periodo_err_s': 0.00675, 'frecuencia_Hz': 0.09999, 'frecuencia_err_Hz': 6.7e-05, 'jitter_s': 0.02542, 'tolerancia_s': 0.0988, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 11.22, 'tren_fin_s': 61.253, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados  6  ...               3.0954           0.0922
+[1 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
 Columns: [tiempo_s, intervalo_s, frecuencia_Hz]
 Index: [], 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
-0       1       10.8312     10.8177 -0.01348       True
-1       2       20.9378     20.9614  0.02359       True
-2       3       31.0445     31.0378 -0.00674       True
-3       4       41.1511     41.1478 -0.00337       True
-4       5       51.2578     51.2578  0.00000       True}</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>29.67353799876205</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.2050370615496523</v>
-      </c>
-      <c r="O2" t="n">
-        <v>3.587675183283098</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-0.03370005963029143</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>7.35201019796932</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.05770279687534764</v>
+0       1       11.2567     11.2200 -0.03675       True
+1       2       21.2579     21.2867  0.02873       True
+2       3       31.2591     31.2883  0.02921       True
+3       4       41.2603     41.2533 -0.00698       True
+4       5       51.2615     51.2567 -0.00484       True
+5       6       61.2627     61.2533 -0.00937       True}</t>
+        </is>
       </c>
       <c r="S2" t="n">
-        <v>1.748792325527406</v>
+        <v>30.00000000000171</v>
       </c>
       <c r="T2" t="n">
-        <v>2.069048141212145</v>
+        <v>0.1198670296367652</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.51962163580837</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-0.03333333333333144</v>
+      </c>
+      <c r="W2" t="n">
+        <v>3.90471788509889</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.02986361976307547</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.087273142118661</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.9728197199516452</v>
       </c>
     </row>
   </sheetData>
@@ -771,56 +809,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -833,65 +871,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>10.82</v>
+        <v>11.22</v>
       </c>
       <c r="D2" t="n">
-        <v>51.26</v>
+        <v>61.25</v>
       </c>
       <c r="E2" t="n">
-        <v>10.11</v>
+        <v>10.0017</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0169</v>
+        <v>0.0067</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0989</v>
+        <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0893</v>
+        <v>3.0954</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0741</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>estimulados_dudosos</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>61.13</v>
-      </c>
-      <c r="D3" t="n">
-        <v>72.25</v>
-      </c>
-      <c r="E3" t="n">
-        <v>11.121</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.08989999999999999</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.087</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.0584</v>
+        <v>0.0922</v>
       </c>
     </row>
   </sheetData>
@@ -905,31 +909,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -940,13 +944,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>10.8312</v>
+        <v>11.2567</v>
       </c>
       <c r="C2" t="n">
-        <v>10.8177</v>
+        <v>11.22</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.01348</v>
+        <v>-0.03675</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
@@ -957,13 +961,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9378</v>
+        <v>21.2579</v>
       </c>
       <c r="C3" t="n">
-        <v>20.9614</v>
+        <v>21.2867</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02359</v>
+        <v>0.02873</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
@@ -974,13 +978,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>31.0445</v>
+        <v>31.2591</v>
       </c>
       <c r="C4" t="n">
-        <v>31.0378</v>
+        <v>31.2883</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.00674</v>
+        <v>0.02921</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
@@ -991,13 +995,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>41.1511</v>
+        <v>41.2603</v>
       </c>
       <c r="C5" t="n">
-        <v>41.1478</v>
+        <v>41.2533</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.00337</v>
+        <v>-0.00698</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
@@ -1008,15 +1012,32 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>51.2578</v>
+        <v>51.2615</v>
       </c>
       <c r="C6" t="n">
-        <v>51.2578</v>
+        <v>51.2567</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>-0.00484</v>
       </c>
       <c r="E6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>61.2627</v>
+      </c>
+      <c r="C7" t="n">
+        <v>61.2533</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.00937</v>
+      </c>
+      <c r="E7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1031,21 +1052,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
@@ -1056,10 +1077,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>10.81771914132379</v>
+        <v>11.22</v>
       </c>
       <c r="C2" t="n">
-        <v>3.047900000000027</v>
+        <v>3.072699999999941</v>
       </c>
     </row>
     <row r="3">
@@ -1067,10 +1088,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>20.96143709004174</v>
+        <v>21.28666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>3.128900000000044</v>
+        <v>3.15440000000001</v>
       </c>
     </row>
     <row r="4">
@@ -1078,10 +1099,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>31.03775491949911</v>
+        <v>31.28833333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>3.08929999999998</v>
+        <v>3.127700000000004</v>
       </c>
     </row>
     <row r="5">
@@ -1089,10 +1110,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>41.14777280858677</v>
+        <v>41.25333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>3.121999999999957</v>
+        <v>3.118200000000002</v>
       </c>
     </row>
     <row r="6">
@@ -1100,10 +1121,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>51.25779069767442</v>
+        <v>51.25666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>2.959799999999973</v>
+        <v>2.925799999999981</v>
       </c>
     </row>
     <row r="7">
@@ -1111,21 +1132,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>61.13190816935003</v>
+        <v>61.25333333333334</v>
       </c>
       <c r="C7" t="n">
-        <v>3.145399999999995</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>72.25292784734646</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1.028699999999958</v>
+        <v>3.019999999999982</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_583_EXP6_CTRL" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_583_EXP6_CTR" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_583_EXP6_CTR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_583_EXP6_CTR" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -565,7 +566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AR2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,6 +698,96 @@
       <c r="Z1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
         </is>
       </c>
     </row>
@@ -796,6 +887,68 @@
       </c>
       <c r="Z2" t="n">
         <v>0.9728197199516452</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.309524275274353</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1.283-1.322</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.2578112034419462</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.2541-0.2808</t>
+        </is>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.1291666666666709</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1810278981632827</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0.1589-0.1844</t>
+        </is>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.09916666666666529</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.3008333333333342</v>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>TTP y RT50 medibles</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1141,4 +1294,550 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>320</v>
+      </c>
+      <c r="D2" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.072699999999941</v>
+      </c>
+      <c r="F2" t="n">
+        <v>236.4120570482098</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.299722204681527</v>
+      </c>
+      <c r="H2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>10.99516567312469</v>
+      </c>
+      <c r="J2" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2248343268753139</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1300000000000008</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3683333333333394</v>
+      </c>
+      <c r="N2" t="b">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>7</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.2227906568317479</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0666666666666611</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.2999999999999989</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>11.57682268563163</v>
+      </c>
+      <c r="U2" t="n">
+        <v>18</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5816570125069465</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>622</v>
+      </c>
+      <c r="D3" t="n">
+        <v>21.28666666666667</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3.15440000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>236.3805482885457</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.33445836505527</v>
+      </c>
+      <c r="H3" t="n">
+        <v>5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20.99902982187475</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.2876368447919226</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.128333333333341</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.370000000000001</v>
+      </c>
+      <c r="N3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.1515656249999928</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.06333333333333968</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2999999999999901</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>21.5769019607843</v>
+      </c>
+      <c r="U3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5778721389095587</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>922</v>
+      </c>
+      <c r="D4" t="n">
+        <v>31.28833333333333</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.127700000000004</v>
+      </c>
+      <c r="F4" t="n">
+        <v>236.3647913522251</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.323251226253567</v>
+      </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>30.99729975162994</v>
+      </c>
+      <c r="J4" t="n">
+        <v>9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.2910335817033953</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1316666666666713</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3316666666666599</v>
+      </c>
+      <c r="N4" t="b">
+        <v>1</v>
+      </c>
+      <c r="O4" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1453174834694764</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3016666666666694</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>31.59239592378196</v>
+      </c>
+      <c r="U4" t="n">
+        <v>19</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5950961721520294</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1221</v>
+      </c>
+      <c r="D5" t="n">
+        <v>41.25333333333334</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3.118200000000002</v>
+      </c>
+      <c r="F5" t="n">
+        <v>236.3478914650523</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.319326345867179</v>
+      </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>40.99959028760019</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.2537430457331453</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.1300000000000097</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3299999999999983</v>
+      </c>
+      <c r="N5" t="b">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1854311543810852</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.2999999999999901</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>41.57972653205808</v>
+      </c>
+      <c r="U5" t="n">
+        <v>18</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5801362444578899</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1521</v>
+      </c>
+      <c r="D6" t="n">
+        <v>51.25666666666667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2.925799999999981</v>
+      </c>
+      <c r="F6" t="n">
+        <v>236.2883785333899</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.2382327129925</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>50.99636048830894</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.2603061783577232</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.336666666666666</v>
+      </c>
+      <c r="N6" t="b">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>6</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.1808406407108691</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>51.55164392764858</v>
+      </c>
+      <c r="U6" t="n">
+        <v>17</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5552834393396324</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1813</v>
+      </c>
+      <c r="D7" t="n">
+        <v>61.25333333333334</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.019999999999982</v>
+      </c>
+      <c r="F7" t="n">
+        <v>236.308600690735</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.277989878985555</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>60.99801710480717</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.2553162285261692</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.1812151556156962</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>61.60161535994869</v>
+      </c>
+      <c r="U7" t="n">
+        <v>19</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6035982551415202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,107 +451,317 @@
         <v>0.2175</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.29</v>
+        <v>0.2392</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>3.63</v>
       </c>
       <c r="B4" t="n">
-        <v>0.435</v>
+        <v>0.2632</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>3.993</v>
       </c>
       <c r="B5" t="n">
-        <v>0.58</v>
+        <v>0.2895</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>10</v>
+        <v>4.392</v>
       </c>
       <c r="B6" t="n">
-        <v>0.725</v>
+        <v>0.3184</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>4.832</v>
       </c>
       <c r="B7" t="n">
-        <v>0.87</v>
+        <v>0.3503</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15</v>
+        <v>5.315</v>
       </c>
       <c r="B8" t="n">
-        <v>1.0875</v>
+        <v>0.3853</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>5.846</v>
       </c>
       <c r="B9" t="n">
-        <v>1.45</v>
+        <v>0.4238</v>
       </c>
       <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="n">
         <v>6</v>
       </c>
-      <c r="D9" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6.431</v>
+      </c>
+      <c r="B10" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7.074</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.5129</v>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7.781</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5641</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>8.558999999999999</v>
+      </c>
+      <c r="B13" t="n">
+        <v>0.6205000000000001</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>9.414999999999999</v>
+      </c>
+      <c r="B14" t="n">
+        <v>0.6826</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10.357</v>
+      </c>
+      <c r="B15" t="n">
+        <v>0.7509</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11.392</v>
+      </c>
+      <c r="B16" t="n">
+        <v>0.8259</v>
+      </c>
+      <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>12.532</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.9086</v>
+      </c>
+      <c r="C17" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>13.785</v>
+      </c>
+      <c r="B18" t="n">
+        <v>0.9994</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>15.163</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1.0993</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>16.68</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1.2093</v>
+      </c>
+      <c r="C20" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>18.348</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.3302</v>
+      </c>
+      <c r="C21" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20.182</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1.4632</v>
+      </c>
+      <c r="C22" t="n">
+        <v>6</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22.201</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1.6096</v>
+      </c>
+      <c r="C23" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>24.421</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1.7705</v>
+      </c>
+      <c r="C24" t="n">
+        <v>6</v>
+      </c>
+      <c r="D24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -566,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AR2"/>
+  <dimension ref="A1:BB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,152 +852,202 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>picos_con_sep_menor</t>
+          <t>intervalo_mediano_s</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>intervalo_mediano_s</t>
+          <t>amplitud_traslacion_px</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>amplitud_traslacion_px</t>
+          <t>ritmo</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>ritmo</t>
+          <t>fps_medido</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>fps_medido</t>
+          <t>adelgazamiento_px</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>adelgazamiento_px</t>
+          <t>adelgazamiento_sigma</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>adelgazamiento_sigma</t>
+          <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>retardo_adelgazamiento_s</t>
+          <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>cociente_adelg_trasl_pct</t>
+          <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>adelgazamiento_robusto_px</t>
+          <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>adelgazamiento_robusto_sigma</t>
+          <t>cociente_robusto_pct</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>cociente_robusto_pct</t>
+          <t>cinetica_min_frames</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>cinetica_min_frames</t>
+          <t>amplitud_relativa_pct</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>amplitud_relativa_pct</t>
+          <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>amplitud_relativa_iqr_pct</t>
+          <t>ttp_n_eventos</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>ttp_n_eventos</t>
+          <t>ttp_frames_mediana</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>ttp_frames_mediana</t>
+          <t>ttp_reportable</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>ttp_reportable</t>
+          <t>ttp_s</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>ttp_s</t>
+          <t>ttp_iqr_s</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>ttp_iqr_s</t>
+          <t>ttp_cota_inf_s</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>ttp_cota_inf_s</t>
+          <t>ttp_cota_sup_s</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>ttp_cota_sup_s</t>
+          <t>rt50_n_eventos</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>rt50_n_eventos</t>
+          <t>rt50_frames_mediana</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>rt50_frames_mediana</t>
+          <t>rt50_reportable</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>rt50_reportable</t>
+          <t>rt50_s</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>rt50_s</t>
+          <t>rt50_iqr_s</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>rt50_iqr_s</t>
+          <t>rt50_cota_inf_s</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>rt50_cota_inf_s</t>
+          <t>rt50_cota_sup_s</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>rt50_cota_sup_s</t>
+          <t>cinetica_motivo</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>cinetica_motivo</t>
+          <t>fotogramas_sin_medida</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>fotogramas_sin_medida_pct</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>fotogramas_low_quality</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>eventos_junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>win_s_usado</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>win_s_automatico</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>duracion_evento_max_s</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>ventana_corta</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>conteo_por_ventana</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>conteo_estable_ventana</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>mesetas</t>
         </is>
       </c>
     </row>
@@ -819,7 +1079,7 @@
         <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>16.68</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -829,27 +1089,24 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>meseta de 6 eventos en k=12..20 (3 puntos) con 0 falsos de control</t>
+          <t>meseta de 6 eventos en k=12.532..24.421 (x1.95) con 0 falsos de control</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>12-20</t>
+          <t>12.532-24.421</t>
         </is>
       </c>
       <c r="N2" t="b">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>10.00166666666666</v>
       </c>
       <c r="P2" t="n">
-        <v>10.00166666666666</v>
-      </c>
-      <c r="Q2" t="n">
         <v>3.095449999999971</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>{'n_eventos': 6, 'hay_estimulacion': True, 'estimulados': array([0, 1, 2, 3, 4, 5]), 'espontaneos': array([], dtype=int64), 'z': 15.815, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 10.0169, 'periodo_s': 10.00119, 'periodo_err_s': 0.00675, 'frecuencia_Hz': 0.09999, 'frecuencia_err_Hz': 6.7e-05, 'jitter_s': 0.02542, 'tolerancia_s': 0.0988, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 11.22, 'tren_fin_s': 61.253, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
 0  estimulados  6  ...               3.0954           0.0922
@@ -864,90 +1121,127 @@
 5       6       61.2627     61.2533 -0.00937       True}</t>
         </is>
       </c>
+      <c r="R2" t="n">
+        <v>30.00000000000171</v>
+      </c>
       <c r="S2" t="n">
-        <v>30.00000000000171</v>
+        <v>0.1198670296367652</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1198670296367652</v>
+        <v>2.51962163580837</v>
       </c>
       <c r="U2" t="n">
-        <v>2.51962163580837</v>
+        <v>-0.03333333333333144</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.03333333333333144</v>
+        <v>3.90471788509889</v>
       </c>
       <c r="W2" t="n">
-        <v>3.90471788509889</v>
+        <v>0.02986361976307547</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02986361976307547</v>
+        <v>1.087273142118661</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.087273142118661</v>
+        <v>0.9728197199516452</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9728197199516452</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB2" t="n">
         <v>1.309524275274353</v>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>1.283-1.322</t>
         </is>
       </c>
+      <c r="AC2" t="n">
+        <v>6</v>
+      </c>
       <c r="AD2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.2578112034419462</v>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.2541-0.2808</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1291666666666709</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>6</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0.2578112034419462</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0.2541-0.2808</t>
-        </is>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.1291666666666709</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0.3350000000000009</v>
       </c>
       <c r="AK2" t="n">
         <v>6</v>
       </c>
-      <c r="AL2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AN2" t="n">
+      <c r="AL2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM2" t="n">
         <v>0.1810278981632827</v>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.1589-0.1844</t>
         </is>
       </c>
+      <c r="AO2" t="n">
+        <v>0.09916666666666529</v>
+      </c>
       <c r="AP2" t="n">
-        <v>0.09916666666666529</v>
-      </c>
-      <c r="AQ2" t="n">
         <v>0.3008333333333342</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0.5999999999999659</v>
+      </c>
+      <c r="AY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>1.5 s: 6 | 2 s: 6 | 3 s: 6</t>
+        </is>
+      </c>
+      <c r="BA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>6 ev en k=12.532-24.421</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1224,6 +1518,11 @@
           <t>amplitud_px</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>junto_a_hueco</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -1234,6 +1533,9 @@
       </c>
       <c r="C2" t="n">
         <v>3.072699999999941</v>
+      </c>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1246,6 +1548,9 @@
       <c r="C3" t="n">
         <v>3.15440000000001</v>
       </c>
+      <c r="D3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1257,6 +1562,9 @@
       <c r="C4" t="n">
         <v>3.127700000000004</v>
       </c>
+      <c r="D4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1268,6 +1576,9 @@
       <c r="C5" t="n">
         <v>3.118200000000002</v>
       </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1279,6 +1590,9 @@
       <c r="C6" t="n">
         <v>2.925799999999981</v>
       </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1289,6 +1603,9 @@
       </c>
       <c r="C7" t="n">
         <v>3.019999999999982</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
@@ -1,18 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="estab_Video_583_EXP6_CTRL4" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="resumen_Video_583_EXP6_CTR" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ritmo_Video_583_EXP6_CTRL" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="grilla_Video_583_EXP6_CTR" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="eventos_Video_583_EXP6_CTR" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cinetica_Video_583_EXP6_CTR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="estab_Video_583_EXP6_CTRL4" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="resumen_Video_583_EXP6_CTR" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ritmo_Video_583_EXP6_CTRL" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="trenes_Video_583_EXP6_CTR" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="grilla_Video_583_EXP6_CTR" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="eventos_Video_583_EXP6_CTR" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="cinetica_Video_583_EXP6_CTR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="cin_grupos_Video_583_EXP6_C" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +24,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +44,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,12 +52,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,22 +436,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -776,278 +790,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB2"/>
+  <dimension ref="A1:BI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_grupo_principal</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>mesetas</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>ruido_borde_sup_px</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>ruido_borde_inf_px</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>cociente_ruido_bordes</t>
         </is>
       </c>
     </row>
@@ -1108,17 +1157,24 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'n_eventos': 6, 'hay_estimulacion': True, 'estimulados': array([0, 1, 2, 3, 4, 5]), 'espontaneos': array([], dtype=int64), 'z': 15.815, 'p_valor': 0.004975124378109453, 'periodo_grilla_s': 10.0169, 'periodo_s': 10.00119, 'periodo_err_s': 0.00675, 'frecuencia_Hz': 0.09999, 'frecuencia_err_Hz': 6.7e-05, 'jitter_s': 0.02542, 'tolerancia_s': 0.0988, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 11.22, 'tren_fin_s': 61.253, 'estimulados_dudosos': array([], dtype=int64), 'resumen_grupos':          grupo  n  ...  amplitud_mediana_px  amplitud_IQR_px
-0  estimulados  6  ...               3.0954           0.0922
+          <t>{'n_eventos': 6, 'fuente_tiempo': 'inicio (onset 10 %) en 6 de 6 eventos; pico en el resto', 'modo_busqueda': 'dirigida', 'trenes':    tren           busqueda  ... inicio_s   fin_s
+0     1  dirigida a 0.1 Hz  ...   10.995  60.998
+[1 rows x 17 columns], 'dudosos': Empty DataFrame
+Columns: []
+Index: [], 'sacados_tiempo_amplitud': Empty DataFrame
+Columns: []
+Index: [], 'grupo_por_evento': array(['estimulados', 'estimulados', 'estimulados', 'estimulados',
+       'estimulados', 'estimulados'], dtype=object), 'tren_por_evento': array([1, 1, 1, 1, 1, 1]), 'estimulados': array([0, 1, 2, 3, 4, 5]), 'estimulados_dudosos': array([], dtype=int64), 'espontaneos': array([], dtype=int64), 'hay_estimulacion': True, 'n_trenes_estimulados': 1, 'tren_principal': 1, 'veredicto': 'enganchado a la frecuencia configurada (0.1 Hz)', 'z': 19.288, 'p_valor': 0.000999000999000999, 'periodo_grilla_s': 9.9782, 'periodo_s': 10.00024, 'periodo_err_s': 0.0023, 'frecuencia_Hz': 0.1, 'frecuencia_err_Hz': 2.3e-05, 'jitter_s': np.float64(0.00962), 'tolerancia_s': 0.0667, 'n_estimulados': 6, 'n_ranuras': 6, 'tasa_captura_pct': 100.0, 'tren_inicio_s': 10.995, 'tren_fin_s': 60.998, 'jitter_limitado_por_resolucion': True, 'resumen_grupos':          grupo  n  t_inicio_s  ...  CV_intervalo_pct  amplitud_mediana_px  amplitud_IQR_px
+0  estimulados  6        11.0  ...               0.0               3.0954           0.0922
 [1 rows x 10 columns], 'espontaneas_instantanea': Empty DataFrame
 Columns: [tiempo_s, intervalo_s, frecuencia_Hz]
-Index: [], 'grilla':    ranura  t_esperado_s  t_medido_s  error_s  capturada
-0       1       11.2567     11.2200 -0.03675       True
-1       2       21.2579     21.2867  0.02873       True
-2       3       31.2591     31.2883  0.02921       True
-3       4       41.2603     41.2533 -0.00698       True
-4       5       51.2615     51.2567 -0.00484       True
-5       6       61.2627     61.2533 -0.00937       True}</t>
+Index: [], 'grilla':    tren  ranura  t_esperado_s  t_medido_s  error_s  capturada
+0     1       1       10.9970     10.9952 -0.00180       True
+1     1       2       20.9972     20.9990  0.00182       True
+2     1       3       30.9975     30.9973 -0.00016       True
+3     1       4       40.9977     40.9996  0.00189       True
+4     1       5       50.9979     50.9964 -0.00158       True
+5     1       6       60.9982     60.9980 -0.00017       True}</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -1137,112 +1193,135 @@
         <v>3.90471788509889</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02986361976307547</v>
+        <v>0.02986361976307074</v>
       </c>
       <c r="X2" t="n">
-        <v>1.087273142118661</v>
+        <v>1.087273142118488</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9728197199516452</v>
-      </c>
-      <c r="Z2" t="n">
+        <v>0.9728197199514909</v>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="AA2" t="n">
         <v>5</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC2" t="n">
         <v>1.309524275274353</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1.283-1.322</t>
         </is>
       </c>
-      <c r="AC2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AE2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG2" t="n">
         <v>8</v>
       </c>
-      <c r="AE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="AH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.2578112034419462</v>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>0.2541-0.2808</t>
         </is>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>0.1291666666666709</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>0.3350000000000009</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL2" t="b">
-        <v>1</v>
-      </c>
       <c r="AM2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>0.1810278981632827</v>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>0.1589-0.1844</t>
         </is>
       </c>
-      <c r="AO2" t="n">
+      <c r="AS2" t="n">
         <v>0.09916666666666529</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>0.3008333333333342</v>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>TTP y RT50 medibles</t>
         </is>
       </c>
-      <c r="AR2" t="n">
+      <c r="AV2" t="n">
         <v>0</v>
       </c>
-      <c r="AS2" t="n">
+      <c r="AW2" t="n">
         <v>0</v>
       </c>
-      <c r="AT2" t="n">
+      <c r="AX2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>0</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>2</v>
       </c>
-      <c r="AW2" t="b">
-        <v>1</v>
-      </c>
-      <c r="AX2" t="n">
+      <c r="BA2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BB2" t="n">
         <v>0.5999999999999659</v>
       </c>
-      <c r="AY2" t="b">
+      <c r="BC2" t="b">
         <v>0</v>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>1.5 s: 6 | 2 s: 6 | 3 s: 6</t>
         </is>
       </c>
-      <c r="BA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BE2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>6 ev en k=12.532-24.421</t>
         </is>
+      </c>
+      <c r="BG2" t="n">
+        <v>0.1061541600000265</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>0.07820715000000472</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.357345971564238</v>
       </c>
     </row>
   </sheetData>
@@ -1260,52 +1339,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1321,22 +1400,22 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>61.25</v>
+        <v>61</v>
       </c>
       <c r="E2" t="n">
         <v>10.0017</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0067</v>
+        <v>0.004</v>
       </c>
       <c r="G2" t="n">
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
         <v>3.0954</v>
@@ -1356,33 +1435,93 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>ranura</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>t_esperado_s</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>t_medido_s</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>error_s</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>capturada</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>busqueda</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>veredicto</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>clasificacion</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>periodo_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>periodo_err_s</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>frecuencia_Hz</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>jitter_ms</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>z</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>p_valor</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_tren</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>n_ranuras</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>captura_pct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>n_dudosos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>n_sacados_tiempo_amplitud</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>inicio_s</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>fin_s</t>
         </is>
       </c>
     </row>
@@ -1390,102 +1529,59 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
-        <v>11.2567</v>
-      </c>
-      <c r="C2" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.03675</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>21.2579</v>
-      </c>
-      <c r="C3" t="n">
-        <v>21.2867</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.02873</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>31.2591</v>
-      </c>
-      <c r="C4" t="n">
-        <v>31.2883</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.02921</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>41.2603</v>
-      </c>
-      <c r="C5" t="n">
-        <v>41.2533</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-0.00698</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>51.2615</v>
-      </c>
-      <c r="C6" t="n">
-        <v>51.2567</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-0.00484</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>61.2627</v>
-      </c>
-      <c r="C7" t="n">
-        <v>61.2533</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.00937</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>dirigida a 0.1 Hz</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>enganchado a la frecuencia configurada (0.1 Hz)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>10.00024</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0023</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="I2" t="n">
+        <v>19.288</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.000999000999000999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>100</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>10.995</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>60.998</v>
       </c>
     </row>
   </sheetData>
@@ -1499,28 +1595,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>evento</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>tiempo_s</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>amplitud_px</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>junto_a_hueco</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ranura</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>t_esperado_s</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>t_medido_s</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>error_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>capturada</t>
         </is>
       </c>
     </row>
@@ -1529,83 +1635,119 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>11.22</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.072699999999941</v>
-      </c>
-      <c r="D2" t="b">
-        <v>0</v>
+        <v>10.997</v>
+      </c>
+      <c r="D2" t="n">
+        <v>10.9952</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.0018</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>21.28666666666667</v>
-      </c>
       <c r="C3" t="n">
-        <v>3.15440000000001</v>
-      </c>
-      <c r="D3" t="b">
-        <v>0</v>
+        <v>20.9972</v>
+      </c>
+      <c r="D3" t="n">
+        <v>20.999</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00182</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
-        <v>31.28833333333333</v>
-      </c>
       <c r="C4" t="n">
-        <v>3.127700000000004</v>
-      </c>
-      <c r="D4" t="b">
-        <v>0</v>
+        <v>30.9975</v>
+      </c>
+      <c r="D4" t="n">
+        <v>30.9973</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.00016</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
-        <v>41.25333333333334</v>
-      </c>
       <c r="C5" t="n">
-        <v>3.118200000000002</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
+        <v>40.9977</v>
+      </c>
+      <c r="D5" t="n">
+        <v>40.9996</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.00189</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
-        <v>51.25666666666667</v>
-      </c>
       <c r="C6" t="n">
-        <v>2.925799999999981</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
+        <v>50.9979</v>
+      </c>
+      <c r="D6" t="n">
+        <v>50.9964</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.00158</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>61.25333333333334</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>3.019999999999982</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
+        <v>60.9982</v>
+      </c>
+      <c r="D7" t="n">
+        <v>60.998</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.00017</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1619,118 +1761,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>grupo</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>frame_pico</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>grosor_reposo_px</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>amplitud_relativa_pct</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>meseta_pico_frames</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>onset_s</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>ttp_frames</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ttp_s</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ttp_min_s</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>ttp_max_s</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>ttp_medible</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>rt50_frames</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>rt50_s</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>rt50_min_s</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>rt50_max_s</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>rt50_medible</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>offset_s</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>duracion_frames</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>duracion_s</t>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>junto_a_hueco</t>
         </is>
       </c>
     </row>
@@ -1738,420 +1790,935 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B2" t="n">
+        <v>11.22</v>
       </c>
       <c r="C2" t="n">
-        <v>320</v>
-      </c>
-      <c r="D2" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="E2" t="n">
         <v>3.072699999999941</v>
       </c>
-      <c r="F2" t="n">
-        <v>236.4120570482098</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.299722204681527</v>
-      </c>
-      <c r="H2" t="n">
-        <v>5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>10.99516567312469</v>
-      </c>
-      <c r="J2" t="n">
-        <v>7</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0.2248343268753139</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.1300000000000008</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.3683333333333394</v>
-      </c>
-      <c r="N2" t="b">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>7</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.2227906568317479</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.0666666666666611</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.2999999999999989</v>
-      </c>
-      <c r="S2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T2" t="n">
-        <v>11.57682268563163</v>
-      </c>
-      <c r="U2" t="n">
-        <v>18</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0.5816570125069465</v>
+      <c r="D2" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B3" t="n">
+        <v>21.28666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>622</v>
-      </c>
-      <c r="D3" t="n">
-        <v>21.28666666666667</v>
-      </c>
-      <c r="E3" t="n">
         <v>3.15440000000001</v>
       </c>
-      <c r="F3" t="n">
-        <v>236.3805482885457</v>
-      </c>
-      <c r="G3" t="n">
-        <v>1.33445836505527</v>
-      </c>
-      <c r="H3" t="n">
-        <v>5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>20.99902982187475</v>
-      </c>
-      <c r="J3" t="n">
-        <v>9</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.2876368447919226</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.128333333333341</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.370000000000001</v>
-      </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>5</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.1515656249999928</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.06333333333333968</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.2999999999999901</v>
-      </c>
-      <c r="S3" t="b">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>21.5769019607843</v>
-      </c>
-      <c r="U3" t="n">
-        <v>18</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0.5778721389095587</v>
+      <c r="D3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B4" t="n">
+        <v>31.28833333333333</v>
       </c>
       <c r="C4" t="n">
-        <v>922</v>
-      </c>
-      <c r="D4" t="n">
-        <v>31.28833333333333</v>
-      </c>
-      <c r="E4" t="n">
         <v>3.127700000000004</v>
       </c>
-      <c r="F4" t="n">
-        <v>236.3647913522251</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.323251226253567</v>
-      </c>
-      <c r="H4" t="n">
-        <v>4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>30.99729975162994</v>
-      </c>
-      <c r="J4" t="n">
-        <v>9</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.2910335817033953</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.1316666666666713</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.3316666666666599</v>
-      </c>
-      <c r="N4" t="b">
-        <v>1</v>
-      </c>
-      <c r="O4" t="n">
-        <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.1453174834694764</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.3016666666666694</v>
-      </c>
-      <c r="S4" t="b">
-        <v>1</v>
-      </c>
-      <c r="T4" t="n">
-        <v>31.59239592378196</v>
-      </c>
-      <c r="U4" t="n">
-        <v>19</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0.5950961721520294</v>
+      <c r="D4" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B5" t="n">
+        <v>41.25333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>1221</v>
-      </c>
-      <c r="D5" t="n">
-        <v>41.25333333333334</v>
-      </c>
-      <c r="E5" t="n">
         <v>3.118200000000002</v>
       </c>
-      <c r="F5" t="n">
-        <v>236.3478914650523</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.319326345867179</v>
-      </c>
-      <c r="H5" t="n">
-        <v>4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>40.99959028760019</v>
-      </c>
-      <c r="J5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0.2537430457331453</v>
-      </c>
-      <c r="L5" t="n">
-        <v>0.1300000000000097</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.3299999999999983</v>
-      </c>
-      <c r="N5" t="b">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.1854311543810852</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.2999999999999901</v>
-      </c>
-      <c r="S5" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>41.57972653205808</v>
-      </c>
-      <c r="U5" t="n">
-        <v>18</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.5801362444578899</v>
+      <c r="D5" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>estimulados</t>
-        </is>
+      <c r="B6" t="n">
+        <v>51.25666666666667</v>
       </c>
       <c r="C6" t="n">
-        <v>1521</v>
-      </c>
-      <c r="D6" t="n">
-        <v>51.25666666666667</v>
-      </c>
-      <c r="E6" t="n">
         <v>2.925799999999981</v>
       </c>
-      <c r="F6" t="n">
-        <v>236.2883785333899</v>
-      </c>
-      <c r="G6" t="n">
-        <v>1.2382327129925</v>
-      </c>
-      <c r="H6" t="n">
-        <v>5</v>
-      </c>
-      <c r="I6" t="n">
-        <v>50.99636048830894</v>
-      </c>
-      <c r="J6" t="n">
-        <v>8</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.2603061783577232</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.09833333333332916</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.336666666666666</v>
-      </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>6</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.1808406407108691</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.1000000000000014</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.3333333333333357</v>
-      </c>
-      <c r="S6" t="b">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>51.55164392764858</v>
-      </c>
-      <c r="U6" t="n">
-        <v>17</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.5552834393396324</v>
+      <c r="D6" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
+      <c r="B7" t="n">
+        <v>61.25333333333334</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3.019999999999982</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>evento</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tren</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>frame_pico</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tiempo_s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_px</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>grosor_reposo_px</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>meseta_pico_frames</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>onset_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_frames</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_min_s</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_max_s</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_medible</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_frames</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_min_s</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_max_s</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_medible</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>offset_s</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>duracion_frames</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>duracion_s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>320</v>
+      </c>
+      <c r="E2" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="F2" t="n">
+        <v>3.072699999999941</v>
+      </c>
+      <c r="G2" t="n">
+        <v>236.4120570482098</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.299722204681527</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.99516567312469</v>
+      </c>
+      <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.2248343268753139</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1300000000000008</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.3683333333333394</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.2227906568317479</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0666666666666611</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.2999999999999989</v>
+      </c>
+      <c r="T2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>11.57682268563163</v>
+      </c>
+      <c r="V2" t="n">
+        <v>18</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5816570125069465</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>622</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.28666666666667</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.15440000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>236.3805482885457</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.33445836505527</v>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.99902982187475</v>
+      </c>
+      <c r="K3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2876368447919226</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.128333333333341</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.370000000000001</v>
+      </c>
+      <c r="O3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1515656249999928</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.06333333333333968</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2999999999999901</v>
+      </c>
+      <c r="T3" t="b">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>21.5769019607843</v>
+      </c>
+      <c r="V3" t="n">
+        <v>18</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.5778721389095587</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>922</v>
+      </c>
+      <c r="E4" t="n">
+        <v>31.28833333333333</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.127700000000004</v>
+      </c>
+      <c r="G4" t="n">
+        <v>236.3647913522251</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.323251226253567</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>30.99729975162994</v>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2910335817033953</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.1316666666666713</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.3316666666666599</v>
+      </c>
+      <c r="O4" t="b">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.1453174834694764</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.3016666666666694</v>
+      </c>
+      <c r="T4" t="b">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>31.59239592378196</v>
+      </c>
+      <c r="V4" t="n">
+        <v>19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.5950961721520294</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1221</v>
+      </c>
+      <c r="E5" t="n">
+        <v>41.25333333333334</v>
+      </c>
+      <c r="F5" t="n">
+        <v>3.118200000000002</v>
+      </c>
+      <c r="G5" t="n">
+        <v>236.3478914650522</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.31932634586718</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>40.99959028760019</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2537430457331453</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1300000000000097</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.3299999999999983</v>
+      </c>
+      <c r="O5" t="b">
+        <v>1</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.1854311543810852</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2999999999999901</v>
+      </c>
+      <c r="T5" t="b">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>41.57972653205808</v>
+      </c>
+      <c r="V5" t="n">
+        <v>18</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.5801362444578899</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1521</v>
+      </c>
+      <c r="E6" t="n">
+        <v>51.25666666666667</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2.925799999999981</v>
+      </c>
+      <c r="G6" t="n">
+        <v>236.2883785333899</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.2382327129925</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>50.99636048830894</v>
+      </c>
+      <c r="K6" t="n">
+        <v>8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.2603061783577232</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.09833333333332916</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.336666666666666</v>
+      </c>
+      <c r="O6" t="b">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.1808406407108691</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.1000000000000014</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3333333333333357</v>
+      </c>
+      <c r="T6" t="b">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>51.55164392764858</v>
+      </c>
+      <c r="V6" t="n">
+        <v>17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5552834393396324</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>estimulados</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
         <v>1813</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>61.25333333333334</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>3.019999999999982</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>236.308600690735</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1.277989878985555</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>60.99801710480717</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>8</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>0.2553162285261692</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.1000000000000014</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.3333333333333357</v>
       </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>6</v>
+      <c r="O7" t="b">
+        <v>1</v>
       </c>
       <c r="P7" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q7" t="n">
         <v>0.1812151556156962</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>0.09833333333332916</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.3350000000000009</v>
       </c>
-      <c r="S7" t="b">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
+      <c r="T7" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
         <v>61.60161535994869</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>19</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>0.6035982551415202</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>grupo</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_min_frames</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>n_eventos_cinetica</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_pct</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>amplitud_relativa_iqr_pct</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_eventos</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_n_medibles</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_frames_mediana</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_reportable</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_s</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_iqr_s</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ttp_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_eventos</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_n_medibles</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_frames_mediana</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_reportable</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_s</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_iqr_s</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_inf_s</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>rt50_cota_sup_s</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>cinetica_motivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>todos</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.309524275274353</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.283-1.322</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2578112034419462</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.2541-0.2808</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1291666666666709</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q2" t="b">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.1810278981632827</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0.1589-0.1844</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
+        <v>0.09916666666666529</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.3008333333333342</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>TTP y RT50 medibles</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>estimulados</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.309524275274353</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1.283-1.322</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.2578112034419462</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.2541-0.2808</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1291666666666709</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="N3" t="n">
+        <v>6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.1810278981632827</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0.1589-0.1844</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
+        <v>0.09916666666666529</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3008333333333342</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>TTP y RT50 medibles</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
+++ b/data/processed_data/Video_583_EXP6_CTRL4_40V/contracciones.xlsx
@@ -24,16 +24,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -52,21 +49,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,22 +424,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>k</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>umbral_px</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>eventos</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>falsos_control</t>
         </is>
@@ -790,311 +778,316 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI2"/>
+  <dimension ref="A1:BJ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>fps</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_frames</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>signo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ruido_canal_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ruido_grosor_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>n_eventos</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>k_usado</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>k_automatico</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hay_meseta</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>meseta_motivo</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>meseta_k_rango</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>conteo_reportable</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>amplitud_traslacion_px</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>ritmo</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>fps_medido</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>adelgazamiento_px</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>adelgazamiento_sigma</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>retardo_adelgazamiento_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cociente_adelg_trasl_pct</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_px</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>adelgazamiento_robusto_sigma</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>cociente_robusto_pct</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>cinetica_grupo_principal</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>fotogramas_sin_medida_pct</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>fotogramas_low_quality</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>eventos_junto_a_hueco</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>eventos_junto_al_borde</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
         <is>
           <t>win_s_usado</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>win_s_automatico</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>duracion_evento_max_s</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>ventana_corta</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>conteo_por_ventana</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>conteo_estable_ventana</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>mesetas</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ruido_borde_sup_px</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>ruido_borde_inf_px</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>cociente_ruido_bordes</t>
         </is>
@@ -1290,37 +1283,40 @@
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
         <v>2</v>
       </c>
-      <c r="BA2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BB2" t="n">
+      <c r="BB2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BC2" t="n">
         <v>0.5999999999999659</v>
       </c>
-      <c r="BC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BD2" t="b">
+        <v>0</v>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>1.5 s: 6 | 2 s: 6 | 3 s: 6</t>
         </is>
       </c>
-      <c r="BE2" t="b">
-        <v>1</v>
-      </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG2" t="inlineStr">
         <is>
           <t>6 ev en k=12.532-24.421</t>
         </is>
       </c>
-      <c r="BG2" t="n">
+      <c r="BH2" t="n">
         <v>0.1061541600000265</v>
       </c>
-      <c r="BH2" t="n">
+      <c r="BI2" t="n">
         <v>0.07820715000000472</v>
       </c>
-      <c r="BI2" t="n">
+      <c r="BJ2" t="n">
         <v>1.357345971564238</v>
       </c>
     </row>
@@ -1339,52 +1335,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>n</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_inicio_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_fin_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>intervalo_mediano_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>intervalo_IQR_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_mediana_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>CV_intervalo_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>amplitud_mediana_px</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>amplitud_IQR_px</t>
         </is>
@@ -1439,87 +1435,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>busqueda</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>veredicto</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>clasificacion</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>periodo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>periodo_err_s</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>frecuencia_Hz</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>jitter_ms</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>z</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>p_valor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>n_eventos_tren</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>n_ranuras</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>captura_pct</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>n_dudosos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>n_sacados_tiempo_amplitud</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inicio_s</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>fin_s</t>
         </is>
@@ -1599,32 +1595,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>ranura</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>t_esperado_s</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>t_medido_s</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>error_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>capturada</t>
         </is>
@@ -1761,28 +1757,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>junto_a_hueco</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>junto_al_borde</t>
         </is>
       </c>
     </row>
@@ -1797,6 +1798,9 @@
         <v>3.072699999999941</v>
       </c>
       <c r="D2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1813,6 +1817,9 @@
       <c r="D3" t="b">
         <v>0</v>
       </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1827,6 +1834,9 @@
       <c r="D4" t="b">
         <v>0</v>
       </c>
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1841,6 +1851,9 @@
       <c r="D5" t="b">
         <v>0</v>
       </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1855,6 +1868,9 @@
       <c r="D6" t="b">
         <v>0</v>
       </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1867,6 +1883,9 @@
         <v>3.019999999999982</v>
       </c>
       <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1885,117 +1904,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>evento</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>tren</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>frame_pico</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tiempo_s</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>amplitud_px</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>grosor_reposo_px</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>meseta_pico_frames</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>onset_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_frames</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_min_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ttp_max_s</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ttp_medible</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_min_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_max_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_medible</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>offset_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>duracion_frames</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>duracion_s</t>
         </is>
@@ -2454,112 +2473,112 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>cinetica_min_frames</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>n_eventos_cinetica</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>amplitud_relativa_pct</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>amplitud_relativa_iqr_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ttp_n_eventos</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ttp_n_medibles</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ttp_frames_mediana</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ttp_reportable</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ttp_s</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ttp_iqr_s</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>ttp_cota_inf_s</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ttp_cota_sup_s</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>rt50_n_eventos</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>rt50_n_medibles</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>rt50_frames_mediana</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>rt50_reportable</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>rt50_s</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>rt50_iqr_s</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>rt50_cota_inf_s</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>rt50_cota_sup_s</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>cinetica_motivo</t>
         </is>
